--- a/backend/LPG testing/technoeconomic-inputs-{model}.xlsx
+++ b/backend/LPG testing/technoeconomic-inputs-{model}.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23E31B1B-8B7F-4242-A78D-37423AF2CD5E}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23AE7007-21B2-43ED-93AD-134665CC1402}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="2" r:id="rId1"/>
@@ -37,12 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="18">
   <si>
     <t>Units</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>Inputs</t>
@@ -274,6 +271,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,16 +549,16 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>1</v>
+      <c r="D1" s="4">
+        <v>2020</v>
       </c>
       <c r="E1" s="4">
         <v>2021</v>
@@ -682,13 +683,13 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="8">
         <v>0</v>
@@ -816,13 +817,13 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="8">
         <v>0</v>
@@ -950,147 +951,147 @@
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="C5" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="8">
         <v>0</v>
@@ -1218,13 +1219,13 @@
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1352,13 +1353,13 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="8">
         <v>0</v>
@@ -1486,147 +1487,147 @@
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="10">
         <v>0</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="8">
         <v>0</v>
@@ -1754,13 +1755,13 @@
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="8">
         <v>0</v>
@@ -1888,147 +1889,147 @@
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="8">
         <v>0</v>
@@ -2156,13 +2157,13 @@
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="8">
         <v>0</v>
@@ -2290,13 +2291,13 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="8">
         <v>0</v>
@@ -2424,136 +2425,136 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="10">
         <v>0</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2572,13 +2573,13 @@
   <sheetData>
     <row r="1" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
+      <c r="C1" s="4">
+        <v>2020</v>
       </c>
       <c r="D1" s="4">
         <v>2021</v>
@@ -2703,10 +2704,10 @@
     </row>
     <row r="2" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="8">
         <v>0</v>
@@ -2834,10 +2835,10 @@
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="8">
         <v>0</v>
@@ -2965,141 +2966,141 @@
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -3227,10 +3228,10 @@
     </row>
     <row r="6" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="8">
         <v>0</v>
@@ -3358,10 +3359,10 @@
     </row>
     <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -3489,133 +3490,133 @@
     </row>
     <row r="8" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
